--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.137.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.137.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -879,7 +879,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.137.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.137.xlsx
@@ -422,16 +422,16 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="48" customWidth="1" min="14" max="14"/>
     <col width="48" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.137.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.137.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0137.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0137.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -599,18 +599,18 @@
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L24: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” day of</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L16: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: day of â€” -------he and C. D., the defendant hereinafter</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ORDERS OF JANUARY 1851.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ORDERS OF JANUARY 1851.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L11: isolated marker/symbol line :: 2</t>
@@ -661,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>105</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -670,16 +670,8 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: (And for further relief ; pray subpanaÃ¦na.)</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L17: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: named, carried on the business of -----â€” in co-partner-</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -699,7 +691,7 @@
       </c>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t>L16: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: day of â€” -------he and C. D., the defendant hereinafter</t>
+          <t>L16: punctuation artifact: double/multiple hyphen :: day of — -------he and C. D., the defendant hereinafter</t>
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
@@ -737,16 +729,8 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” except t</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L96: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”except tl</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -766,7 +750,7 @@
       </c>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L17: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: named, carried on the business of -----â€” in co-partner-</t>
+          <t>L17: punctuation artifact: double/multiple hyphen :: named, carried on the business of -----— in co-partner-</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
@@ -786,7 +770,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -801,11 +785,7 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: der an indenture, dated the ---------day of - :â€”,</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -958,7 +938,7 @@
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: der an indenture, dated the ---------day of - :â€”,</t>
+          <t>L114: punctuation artifact: double/multiple hyphen :: der an indenture, dated the ---------day of - :—,</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
@@ -1021,12 +1001,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1065,7 +1045,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
